--- a/etf_holdings/2026-08-28_00993A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-28_00993A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 06:15:27</t>
+          <t>2026-08-28 06:35:37</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 06:15:27</t>
+          <t>2026-08-28 06:35:37</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 06:15:27</t>
+          <t>2026-08-28 06:35:37</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 06:15:27</t>
+          <t>2026-08-28 06:35:37</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 06:15:27</t>
+          <t>2026-08-28 06:35:37</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 06:15:27</t>
+          <t>2026-08-28 06:35:37</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 06:15:27</t>
+          <t>2026-08-28 06:35:37</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 06:15:27</t>
+          <t>2026-08-28 06:35:37</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 06:15:27</t>
+          <t>2026-08-28 06:35:37</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 06:15:27</t>
+          <t>2026-08-28 06:35:37</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 06:15:27</t>
+          <t>2026-08-28 06:35:37</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 06:15:27</t>
+          <t>2026-08-28 06:35:37</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 06:15:27</t>
+          <t>2026-08-28 06:35:37</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 06:15:27</t>
+          <t>2026-08-28 06:35:37</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 06:15:27</t>
+          <t>2026-08-28 06:35:37</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-28 06:15:28</t>
+          <t>2026-08-28 06:35:38</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28 06:15:28</t>
+          <t>2026-08-28 06:35:38</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28 06:15:28</t>
+          <t>2026-08-28 06:35:38</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28 06:15:28</t>
+          <t>2026-08-28 06:35:38</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28 06:15:28</t>
+          <t>2026-08-28 06:35:38</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-28 06:15:28</t>
+          <t>2026-08-28 06:35:38</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-28 06:15:28</t>
+          <t>2026-08-28 06:35:38</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-28 06:15:28</t>
+          <t>2026-08-28 06:35:38</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28 06:15:28</t>
+          <t>2026-08-28 06:35:38</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-28 06:15:28</t>
+          <t>2026-08-28 06:35:38</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-28 06:15:28</t>
+          <t>2026-08-28 06:35:38</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-28 06:15:28</t>
+          <t>2026-08-28 06:35:38</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-28 06:15:28</t>
+          <t>2026-08-28 06:35:38</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-28 06:15:28</t>
+          <t>2026-08-28 06:35:38</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-28 06:15:28</t>
+          <t>2026-08-28 06:35:38</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-28 06:15:29</t>
+          <t>2026-08-28 06:35:40</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28 06:15:29</t>
+          <t>2026-08-28 06:35:40</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28 06:15:29</t>
+          <t>2026-08-28 06:35:40</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28 06:15:29</t>
+          <t>2026-08-28 06:35:40</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28 06:15:29</t>
+          <t>2026-08-28 06:35:40</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28 06:15:29</t>
+          <t>2026-08-28 06:35:40</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28 06:15:29</t>
+          <t>2026-08-28 06:35:40</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-28 06:15:29</t>
+          <t>2026-08-28 06:35:40</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-28 06:15:29</t>
+          <t>2026-08-28 06:35:40</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-28 06:15:29</t>
+          <t>2026-08-28 06:35:40</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 06:15:29</t>
+          <t>2026-08-28 06:35:40</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-28 06:15:29</t>
+          <t>2026-08-28 06:35:40</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-28 06:15:29</t>
+          <t>2026-08-28 06:35:40</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-28 06:15:29</t>
+          <t>2026-08-28 06:35:40</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-28 06:15:29</t>
+          <t>2026-08-28 06:35:40</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-28 06:15:31</t>
+          <t>2026-08-28 06:35:41</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-28 06:15:31</t>
+          <t>2026-08-28 06:35:41</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-28 06:15:31</t>
+          <t>2026-08-28 06:35:41</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-28 06:15:31</t>
+          <t>2026-08-28 06:35:41</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-28 06:15:31</t>
+          <t>2026-08-28 06:35:41</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-28_00993A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-28_00993A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 06:35:37</t>
+          <t>2026-08-28 06:59:32</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 06:35:37</t>
+          <t>2026-08-28 06:59:32</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 06:35:37</t>
+          <t>2026-08-28 06:59:32</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 06:35:37</t>
+          <t>2026-08-28 06:59:32</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 06:35:37</t>
+          <t>2026-08-28 06:59:32</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 06:35:37</t>
+          <t>2026-08-28 06:59:32</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 06:35:37</t>
+          <t>2026-08-28 06:59:32</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 06:35:37</t>
+          <t>2026-08-28 06:59:32</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 06:35:37</t>
+          <t>2026-08-28 06:59:32</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 06:35:37</t>
+          <t>2026-08-28 06:59:32</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 06:35:37</t>
+          <t>2026-08-28 06:59:32</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 06:35:37</t>
+          <t>2026-08-28 06:59:32</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 06:35:37</t>
+          <t>2026-08-28 06:59:32</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 06:35:37</t>
+          <t>2026-08-28 06:59:32</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 06:35:37</t>
+          <t>2026-08-28 06:59:32</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-28 06:35:38</t>
+          <t>2026-08-28 06:59:33</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28 06:35:38</t>
+          <t>2026-08-28 06:59:33</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28 06:35:38</t>
+          <t>2026-08-28 06:59:33</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28 06:35:38</t>
+          <t>2026-08-28 06:59:33</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28 06:35:38</t>
+          <t>2026-08-28 06:59:33</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-28 06:35:38</t>
+          <t>2026-08-28 06:59:33</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-28 06:35:38</t>
+          <t>2026-08-28 06:59:33</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-28 06:35:38</t>
+          <t>2026-08-28 06:59:33</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28 06:35:38</t>
+          <t>2026-08-28 06:59:33</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-28 06:35:38</t>
+          <t>2026-08-28 06:59:33</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-28 06:35:38</t>
+          <t>2026-08-28 06:59:33</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-28 06:35:38</t>
+          <t>2026-08-28 06:59:33</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-28 06:35:38</t>
+          <t>2026-08-28 06:59:33</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-28 06:35:38</t>
+          <t>2026-08-28 06:59:33</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-28 06:35:38</t>
+          <t>2026-08-28 06:59:33</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-28 06:35:40</t>
+          <t>2026-08-28 06:59:34</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28 06:35:40</t>
+          <t>2026-08-28 06:59:34</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28 06:35:40</t>
+          <t>2026-08-28 06:59:34</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28 06:35:40</t>
+          <t>2026-08-28 06:59:34</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28 06:35:40</t>
+          <t>2026-08-28 06:59:34</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28 06:35:40</t>
+          <t>2026-08-28 06:59:34</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28 06:35:40</t>
+          <t>2026-08-28 06:59:34</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-28 06:35:40</t>
+          <t>2026-08-28 06:59:34</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-28 06:35:40</t>
+          <t>2026-08-28 06:59:34</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-28 06:35:40</t>
+          <t>2026-08-28 06:59:34</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 06:35:40</t>
+          <t>2026-08-28 06:59:34</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-28 06:35:40</t>
+          <t>2026-08-28 06:59:34</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-28 06:35:40</t>
+          <t>2026-08-28 06:59:34</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-28 06:35:40</t>
+          <t>2026-08-28 06:59:34</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-28 06:35:40</t>
+          <t>2026-08-28 06:59:34</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-28 06:35:41</t>
+          <t>2026-08-28 06:59:36</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-28 06:35:41</t>
+          <t>2026-08-28 06:59:36</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-28 06:35:41</t>
+          <t>2026-08-28 06:59:36</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-28 06:35:41</t>
+          <t>2026-08-28 06:59:36</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-28 06:35:41</t>
+          <t>2026-08-28 06:59:36</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-28_00993A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-28_00993A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:32</t>
+          <t>2026-08-28 15:44:53</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,16 +509,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-0.21%2410</t>
+          <t>+0.41%2420</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>+0.41%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2410</v>
+        <v>2420</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:32</t>
+          <t>2026-08-28 15:44:53</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -565,38 +565,38 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2383台光電子</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-6.7%5500</t>
+          <t>-5.93%1110</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-5.93%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5500</v>
+        <v>1110</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.42%115,000</t>
+          <t>6.35%566,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.42%</t>
+          <t>6.35%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>115000</v>
+        <v>566000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.46%</t>
+          <t>-0.40%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:32</t>
+          <t>2026-08-28 15:44:53</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,38 +626,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>2383台光電子</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+1.72%1180</t>
+          <t>0%5490</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+1.72%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1180</v>
+        <v>5490</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.21%566,000</t>
+          <t>6.01%115,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.21%</t>
+          <t>6.01%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>566000</v>
+        <v>115000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:32</t>
+          <t>2026-08-28 15:44:53</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+0.99%5090</t>
+          <t>-1.18%5030</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+0.99%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5090</v>
+        <v>5030</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.53%116,000</t>
+          <t>5.61%116,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.53%</t>
+          <t>5.61%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:32</t>
+          <t>2026-08-28 15:44:53</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+5.86%3340</t>
+          <t>+0.6%3360</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+5.86%</t>
+          <t>+0.6%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3340</v>
+        <v>3360</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4.75%159,000</t>
+          <t>5.05%159,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4.75%</t>
+          <t>5.05%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:32</t>
+          <t>2026-08-28 15:44:53</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0%14340</t>
+          <t>-0.28%14300</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>14340</v>
+        <v>14300</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.53%33,000</t>
+          <t>4.50%33,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.53%</t>
+          <t>4.50%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:32</t>
+          <t>2026-08-28 15:44:53</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-5.56%1445</t>
+          <t>+3.11%1490</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-5.56%</t>
+          <t>+3.11%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1445</v>
+        <v>1490</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.46%308,000</t>
+          <t>4.23%308,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.46%</t>
+          <t>4.23%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:32</t>
+          <t>2026-08-28 15:44:53</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>5274信驊科技</t>
+          <t>2408南亞科</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-2.45%15305</t>
+          <t>-0.18%540</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-2.45%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>15305</v>
+        <v>540</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.95%26,600</t>
+          <t>4.03%783,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.95%</t>
+          <t>4.03%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>26600</v>
+        <v>783000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:32</t>
+          <t>2026-08-28 15:44:53</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>5274信驊科技</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-2.03%3865</t>
+          <t>+2.12%15630</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-2.03%</t>
+          <t>+2.12%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>3865</v>
+        <v>15630</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.85%103,000</t>
+          <t>3.87%26,600</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.85%</t>
+          <t>3.87%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>103000</v>
+        <v>26600</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:32</t>
+          <t>2026-08-28 15:44:53</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2408南亞科</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+4.64%541</t>
+          <t>+3.1%3985</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+4.64%</t>
+          <t>+3.1%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>541</v>
+        <v>3985</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.83%783,000</t>
+          <t>3.78%103,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.83%</t>
+          <t>3.78%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>783000</v>
+        <v>103000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:32</t>
+          <t>2026-08-28 15:44:53</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+0.44%6815</t>
+          <t>+5.65%7200</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+0.44%</t>
+          <t>+5.65%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>6815</v>
+        <v>7200</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.60%56,000</t>
+          <t>3.63%56,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.60%</t>
+          <t>3.63%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:32</t>
+          <t>2026-08-28 15:44:53</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,25 +1180,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+3.75%914</t>
+          <t>-1.64%899</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+3.75%</t>
+          <t>-1.64%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>914</v>
+        <v>899</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.97%356,000</t>
+          <t>3.09%356,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.97%</t>
+          <t>3.09%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:32</t>
+          <t>2026-08-28 15:44:53</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+1.7%2090</t>
+          <t>-4.25%1240</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+1.7%</t>
+          <t>-4.25%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2090</v>
+        <v>1240</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.96%152,000</t>
+          <t>3.06%249,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.96%</t>
+          <t>3.06%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>152000</v>
+        <v>249000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:32</t>
+          <t>2026-08-28 15:44:53</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3443創意電子</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-3.35%5920</t>
+          <t>+1.67%2125</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-3.35%</t>
+          <t>+1.67%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>5920</v>
+        <v>2125</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.84%49,000</t>
+          <t>3.02%152,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.84%</t>
+          <t>3.02%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>49000</v>
+        <v>152000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:32</t>
+          <t>2026-08-28 15:44:53</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,25 +1363,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+2.48%186</t>
+          <t>-2.42%181.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+2.48%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>186</v>
+        <v>181.5</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.78%1,619,000</t>
+          <t>2.86%1,619,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.78%</t>
+          <t>2.86%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:33</t>
+          <t>2026-08-28 15:44:55</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>3443創意電子</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+9.75%1295</t>
+          <t>+1.6%6015</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+9.75%</t>
+          <t>+1.6%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1295</v>
+        <v>6015</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.78%249,000</t>
+          <t>2.76%49,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.78%</t>
+          <t>2.76%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>249000</v>
+        <v>49000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:33</t>
+          <t>2026-08-28 15:44:55</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,25 +1485,25 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+1.33%6105</t>
+          <t>+2.38%6250</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+1.33%</t>
+          <t>+2.38%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>6105</v>
+        <v>6250</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.28%40,000</t>
+          <t>2.32%40,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.28%</t>
+          <t>2.32%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:33</t>
+          <t>2026-08-28 15:44:55</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,25 +1546,25 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-1.4%5645</t>
+          <t>+2.48%5785</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>+2.48%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5645</v>
+        <v>5785</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.00%37,000</t>
+          <t>1.98%37,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>1.98%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:33</t>
+          <t>2026-08-28 15:44:55</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,25 +1607,25 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+1.14%1770</t>
+          <t>+3.39%1830</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+1.14%</t>
+          <t>+3.39%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1770</v>
+        <v>1830</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.84%111,000</t>
+          <t>1.87%111,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.87%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:33</t>
+          <t>2026-08-28 15:44:55</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-4.05%118.5</t>
+          <t>+9.98%2260</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-4.05%</t>
+          <t>+9.98%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>118.5</v>
+        <v>2260</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.69%1,442,000</t>
+          <t>1.74%89,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>1.74%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>1442000</v>
+        <v>89000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:33</t>
+          <t>2026-08-28 15:44:55</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,34 +1724,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>7769鴻勁</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+2.49%2055</t>
+          <t>+2.29%6490</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+2.49%</t>
+          <t>+2.29%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2055</v>
+        <v>6490</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.69%89,000</t>
+          <t>1.63%27,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>1.63%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>89000</v>
+        <v>27000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:33</t>
+          <t>2026-08-28 15:44:55</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,25 +1785,25 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>7769鴻勁</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+0.16%6345</t>
+          <t>+9.7%130</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>+9.7%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>6345</v>
+        <v>130</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.62%27,000</t>
+          <t>1.62%1,442,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1812,11 +1812,11 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>27000</v>
+        <v>1442000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:33</t>
+          <t>2026-08-28 15:44:55</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,33 +1851,33 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-0.67%1490</t>
+          <t>-1.34%1470</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-0.67%</t>
+          <t>-1.34%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1490</v>
+        <v>1470</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.33%94,000</t>
+          <t>1.36%95,872</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>1.36%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>94000</v>
+        <v>95872</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:33</t>
+          <t>2026-08-28 15:44:55</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,25 +1912,25 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+3.35%555</t>
+          <t>+7.57%597</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+3.35%</t>
+          <t>+7.57%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>555</v>
+        <v>597</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.25%245,000</t>
+          <t>1.29%245,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:33</t>
+          <t>2026-08-28 15:44:55</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,25 +1973,25 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+2.2%605</t>
+          <t>+2.64%621</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+2.2%</t>
+          <t>+2.64%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>605</v>
+        <v>621</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.13%202,000</t>
+          <t>1.16%202,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.16%</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:33</t>
+          <t>2026-08-28 15:44:55</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,25 +2034,25 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+3.53%3370</t>
+          <t>-1.93%3305</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+3.53%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>3370</v>
+        <v>3305</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.80%26,000</t>
+          <t>0.83%26,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.83%</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:33</t>
+          <t>2026-08-28 15:44:55</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,25 +2095,25 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+1.41%2155</t>
+          <t>-0.23%2150</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+1.41%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2155</v>
+        <v>2150</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.74%37,000</t>
+          <t>0.76%37,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.74%</t>
+          <t>0.76%</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:33</t>
+          <t>2026-08-28 15:44:55</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,25 +2156,25 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+1.59%127.5</t>
+          <t>-0.78%126.5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+1.59%</t>
+          <t>-0.78%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>127.5</v>
+        <v>126.5</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.53%447,000</t>
+          <t>0.54%447,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:33</t>
+          <t>2026-08-28 15:44:55</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2301光寶科技</t>
+          <t>6187萬潤科技</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-1.95%301</t>
+          <t>-4.55%1365</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>-4.55%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>301</v>
+        <v>1365</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.51%176,000</t>
+          <t>0.53%39,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.53%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>176000</v>
+        <v>39000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:33</t>
+          <t>2026-08-28 15:44:55</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>6187萬潤科技</t>
+          <t>2301光寶科技</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+10%1430</t>
+          <t>+5.48%317.5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+10%</t>
+          <t>+5.48%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1430</v>
+        <v>317.5</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.48%39,000</t>
+          <t>0.50%176,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>39000</v>
+        <v>176000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:34</t>
+          <t>2026-08-28 15:44:56</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,16 +2339,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-0.34%86.8</t>
+          <t>-0.35%86.5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-0.34%</t>
+          <t>-0.35%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>86.8</v>
+        <v>86.5</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:34</t>
+          <t>2026-08-28 15:44:56</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,25 +2400,25 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+1.17%433</t>
+          <t>+0.23%434</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+1.17%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.46%113,000</t>
+          <t>0.47%113,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.47%</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:34</t>
+          <t>2026-08-28 15:44:56</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,25 +2461,25 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+0.64%63.2</t>
+          <t>+1.27%64</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>+1.27%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>63.2</v>
+        <v>64</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.46%777,360</t>
+          <t>0.47%777,360</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.47%</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:34</t>
+          <t>2026-08-28 15:44:56</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,25 +2522,25 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+2.63%585</t>
+          <t>+4.27%610</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+2.63%</t>
+          <t>+4.27%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>585</v>
+        <v>610</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.45%83,000</t>
+          <t>0.46%83,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.46%</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:34</t>
+          <t>2026-08-28 15:44:56</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,16 +2583,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-0.31%32.15</t>
+          <t>+1.87%32.75</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>+1.87%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>32.15</v>
+        <v>32.75</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:34</t>
+          <t>2026-08-28 15:44:56</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,16 +2644,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-1.37%179.5</t>
+          <t>-0.84%178</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>179.5</v>
+        <v>178</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:34</t>
+          <t>2026-08-28 15:44:56</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,38 +2700,38 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>3491昇達科技</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+0.51%1990</t>
+          <t>+5.96%1510</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+5.96%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1990</v>
+        <v>1510</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.43%23,000</t>
+          <t>0.45%33,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>23000</v>
+        <v>33000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:34</t>
+          <t>2026-08-28 15:44:56</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,38 +2761,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2890永豐金控</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+0.51%39.35</t>
+          <t>-3.44%1265</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-3.44%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>39.35</v>
+        <v>1265</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.42%1,140,220</t>
+          <t>0.44%35,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.44%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>1140220</v>
+        <v>35000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:34</t>
+          <t>2026-08-28 15:44:56</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,38 +2822,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3491昇達科技</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+5.95%1425</t>
+          <t>+1.01%2010</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+5.95%</t>
+          <t>+1.01%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1425</v>
+        <v>2010</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.42%33,000</t>
+          <t>0.43%23,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>33000</v>
+        <v>23000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:34</t>
+          <t>2026-08-28 15:44:56</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,38 +2883,38 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2368金像電子</t>
+          <t>2890永豐金控</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-0.96%1030</t>
+          <t>+1.14%39.8</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-0.96%</t>
+          <t>+1.14%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1030</v>
+        <v>39.8</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.41%42,000</t>
+          <t>0.43%1,140,220</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>42000</v>
+        <v>1140220</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:34</t>
+          <t>2026-08-28 15:44:56</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,38 +2944,38 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>3264欣銓</t>
+          <t>2368金像電子</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+0.92%219.5</t>
+          <t>+9.71%1130</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+0.92%</t>
+          <t>+9.71%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>219.5</v>
+        <v>1130</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.40%196,000</t>
+          <t>0.41%42,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>196000</v>
+        <v>42000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:34</t>
+          <t>2026-08-28 15:44:56</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,38 +3005,38 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>3264欣銓</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+9.62%1310</t>
+          <t>+7.06%235</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+9.62%</t>
+          <t>+7.06%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1310</v>
+        <v>235</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.40%35,000</t>
+          <t>0.41%196,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>35000</v>
+        <v>196000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:34</t>
+          <t>2026-08-28 15:44:56</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,38 +3066,38 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2395研華</t>
+          <t>8358金居開發</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-1.89%675</t>
+          <t>+9.92%543</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-1.89%</t>
+          <t>+9.92%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>675</v>
+        <v>543</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.39%60,000</t>
+          <t>0.41%88,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>60000</v>
+        <v>88000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:34</t>
+          <t>2026-08-28 15:44:56</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,38 +3127,38 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>6196帆宣</t>
+          <t>6584南俊國際</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-0.5%497.5</t>
+          <t>+10%682</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>+10%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>497.5</v>
+        <v>682</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.38%80,000</t>
+          <t>0.39%66,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>80000</v>
+        <v>66000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:34</t>
+          <t>2026-08-28 15:44:56</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,25 +3188,25 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>6584南俊國際</t>
+          <t>1560中砂</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+2.65%620</t>
+          <t>+0.72%695</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+2.65%</t>
+          <t>+0.72%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>620</v>
+        <v>695</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.38%66,000</t>
+          <t>0.38%58,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3215,11 +3215,11 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>66000</v>
+        <v>58000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:36</t>
+          <t>2026-08-28 15:44:57</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3249,38 +3249,38 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1560中砂</t>
+          <t>2395研華</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+1.17%690</t>
+          <t>-0.89%669</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+1.17%</t>
+          <t>-0.89%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>690</v>
+        <v>669</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.37%58,000</t>
+          <t>0.38%60,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>58000</v>
+        <v>60000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:36</t>
+          <t>2026-08-28 15:44:57</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3310,38 +3310,38 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>6139亞翔工程</t>
+          <t>6196帆宣</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-2%784</t>
+          <t>-1.01%492.5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-1.01%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>784</v>
+        <v>492.5</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.37%49,000</t>
+          <t>0.38%80,000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>49000</v>
+        <v>80000</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:36</t>
+          <t>2026-08-28 15:44:57</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3371,25 +3371,25 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>6213聯茂</t>
+          <t>6139亞翔工程</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-3.43%563</t>
+          <t>-1.15%775</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-3.43%</t>
+          <t>-1.15%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>563</v>
+        <v>775</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.37%67,000</t>
+          <t>0.37%49,000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3398,11 +3398,11 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>67000</v>
+        <v>49000</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:36</t>
+          <t>2026-08-28 15:44:57</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3432,38 +3432,38 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>8358金居開發</t>
+          <t>6213聯茂</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>+9.9%494</t>
+          <t>+3.37%582</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>+9.9%</t>
+          <t>+3.37%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>494</v>
+        <v>582</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.37%88,000</t>
+          <t>0.36%67,000</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.36%</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>88000</v>
+        <v>67000</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:36</t>
+          <t>2026-08-28 15:44:57</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,25 +3498,25 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-2.27%3870</t>
+          <t>+5.04%4065</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-2.27%</t>
+          <t>+5.04%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>3870</v>
+        <v>4065</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.34%9,000</t>
+          <t>0.33%9,000</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.33%</t>
         </is>
       </c>
       <c r="K51" t="n">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">

--- a/etf_holdings/2026-08-28_00993A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-28_00993A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:53</t>
+          <t>2026-08-28 17:26:50</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:53</t>
+          <t>2026-08-28 17:26:50</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:53</t>
+          <t>2026-08-28 17:26:50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:53</t>
+          <t>2026-08-28 17:26:50</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:53</t>
+          <t>2026-08-28 17:26:50</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:53</t>
+          <t>2026-08-28 17:26:50</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:53</t>
+          <t>2026-08-28 17:26:50</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:53</t>
+          <t>2026-08-28 17:26:50</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:53</t>
+          <t>2026-08-28 17:26:50</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:53</t>
+          <t>2026-08-28 17:26:50</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:53</t>
+          <t>2026-08-28 17:26:50</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:53</t>
+          <t>2026-08-28 17:26:50</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:53</t>
+          <t>2026-08-28 17:26:50</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:53</t>
+          <t>2026-08-28 17:26:50</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:53</t>
+          <t>2026-08-28 17:26:50</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:55</t>
+          <t>2026-08-28 17:26:51</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:55</t>
+          <t>2026-08-28 17:26:51</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:55</t>
+          <t>2026-08-28 17:26:51</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:55</t>
+          <t>2026-08-28 17:26:51</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:55</t>
+          <t>2026-08-28 17:26:51</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:55</t>
+          <t>2026-08-28 17:26:51</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:55</t>
+          <t>2026-08-28 17:26:51</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:55</t>
+          <t>2026-08-28 17:26:51</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:55</t>
+          <t>2026-08-28 17:26:51</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:55</t>
+          <t>2026-08-28 17:26:51</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:55</t>
+          <t>2026-08-28 17:26:51</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:55</t>
+          <t>2026-08-28 17:26:51</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:55</t>
+          <t>2026-08-28 17:26:51</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:55</t>
+          <t>2026-08-28 17:26:51</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:55</t>
+          <t>2026-08-28 17:26:51</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:56</t>
+          <t>2026-08-28 17:26:53</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:56</t>
+          <t>2026-08-28 17:26:53</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:56</t>
+          <t>2026-08-28 17:26:53</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:56</t>
+          <t>2026-08-28 17:26:53</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:56</t>
+          <t>2026-08-28 17:26:53</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:56</t>
+          <t>2026-08-28 17:26:53</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:56</t>
+          <t>2026-08-28 17:26:53</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:56</t>
+          <t>2026-08-28 17:26:53</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:56</t>
+          <t>2026-08-28 17:26:53</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:56</t>
+          <t>2026-08-28 17:26:53</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:56</t>
+          <t>2026-08-28 17:26:53</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:56</t>
+          <t>2026-08-28 17:26:53</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:56</t>
+          <t>2026-08-28 17:26:53</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:56</t>
+          <t>2026-08-28 17:26:53</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:56</t>
+          <t>2026-08-28 17:26:53</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:57</t>
+          <t>2026-08-28 17:26:54</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:57</t>
+          <t>2026-08-28 17:26:54</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:57</t>
+          <t>2026-08-28 17:26:54</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:57</t>
+          <t>2026-08-28 17:26:54</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:57</t>
+          <t>2026-08-28 17:26:54</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-28_00993A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-28_00993A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 17:26:50</t>
+          <t>2026-08-28 20:41:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 17:26:50</t>
+          <t>2026-08-28 20:41:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 17:26:50</t>
+          <t>2026-08-28 20:41:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 17:26:50</t>
+          <t>2026-08-28 20:41:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 17:26:50</t>
+          <t>2026-08-28 20:41:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 17:26:50</t>
+          <t>2026-08-28 20:41:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 17:26:50</t>
+          <t>2026-08-28 20:41:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 17:26:50</t>
+          <t>2026-08-28 20:41:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 17:26:50</t>
+          <t>2026-08-28 20:41:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 17:26:50</t>
+          <t>2026-08-28 20:41:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 17:26:50</t>
+          <t>2026-08-28 20:41:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 17:26:50</t>
+          <t>2026-08-28 20:41:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 17:26:50</t>
+          <t>2026-08-28 20:41:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 17:26:50</t>
+          <t>2026-08-28 20:41:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 17:26:50</t>
+          <t>2026-08-28 20:41:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-28 17:26:51</t>
+          <t>2026-08-28 20:41:01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28 17:26:51</t>
+          <t>2026-08-28 20:41:01</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28 17:26:51</t>
+          <t>2026-08-28 20:41:01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28 17:26:51</t>
+          <t>2026-08-28 20:41:01</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28 17:26:51</t>
+          <t>2026-08-28 20:41:01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-28 17:26:51</t>
+          <t>2026-08-28 20:41:01</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-28 17:26:51</t>
+          <t>2026-08-28 20:41:01</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-28 17:26:51</t>
+          <t>2026-08-28 20:41:01</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28 17:26:51</t>
+          <t>2026-08-28 20:41:01</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-28 17:26:51</t>
+          <t>2026-08-28 20:41:01</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-28 17:26:51</t>
+          <t>2026-08-28 20:41:01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-28 17:26:51</t>
+          <t>2026-08-28 20:41:01</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-28 17:26:51</t>
+          <t>2026-08-28 20:41:01</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-28 17:26:51</t>
+          <t>2026-08-28 20:41:01</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-28 17:26:51</t>
+          <t>2026-08-28 20:41:01</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-28 17:26:53</t>
+          <t>2026-08-28 20:41:03</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28 17:26:53</t>
+          <t>2026-08-28 20:41:03</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28 17:26:53</t>
+          <t>2026-08-28 20:41:03</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28 17:26:53</t>
+          <t>2026-08-28 20:41:03</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28 17:26:53</t>
+          <t>2026-08-28 20:41:03</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28 17:26:53</t>
+          <t>2026-08-28 20:41:03</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28 17:26:53</t>
+          <t>2026-08-28 20:41:03</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-28 17:26:53</t>
+          <t>2026-08-28 20:41:03</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-28 17:26:53</t>
+          <t>2026-08-28 20:41:03</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-28 17:26:53</t>
+          <t>2026-08-28 20:41:03</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 17:26:53</t>
+          <t>2026-08-28 20:41:03</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-28 17:26:53</t>
+          <t>2026-08-28 20:41:03</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-28 17:26:53</t>
+          <t>2026-08-28 20:41:03</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-28 17:26:53</t>
+          <t>2026-08-28 20:41:03</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-28 17:26:53</t>
+          <t>2026-08-28 20:41:03</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-28 17:26:54</t>
+          <t>2026-08-28 20:41:04</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-28 17:26:54</t>
+          <t>2026-08-28 20:41:04</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-28 17:26:54</t>
+          <t>2026-08-28 20:41:04</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-28 17:26:54</t>
+          <t>2026-08-28 20:41:04</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-28 17:26:54</t>
+          <t>2026-08-28 20:41:04</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-28_00993A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-28_00993A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 20:41:00</t>
+          <t>2026-08-28 21:42:10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 20:41:00</t>
+          <t>2026-08-28 21:42:10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 20:41:00</t>
+          <t>2026-08-28 21:42:10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 20:41:00</t>
+          <t>2026-08-28 21:42:10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 20:41:00</t>
+          <t>2026-08-28 21:42:10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 20:41:00</t>
+          <t>2026-08-28 21:42:10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 20:41:00</t>
+          <t>2026-08-28 21:42:10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 20:41:00</t>
+          <t>2026-08-28 21:42:10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 20:41:00</t>
+          <t>2026-08-28 21:42:10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 20:41:00</t>
+          <t>2026-08-28 21:42:10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 20:41:00</t>
+          <t>2026-08-28 21:42:10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 20:41:00</t>
+          <t>2026-08-28 21:42:10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 20:41:00</t>
+          <t>2026-08-28 21:42:10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 20:41:00</t>
+          <t>2026-08-28 21:42:10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 20:41:00</t>
+          <t>2026-08-28 21:42:10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-28 20:41:01</t>
+          <t>2026-08-28 21:42:12</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28 20:41:01</t>
+          <t>2026-08-28 21:42:12</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28 20:41:01</t>
+          <t>2026-08-28 21:42:12</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28 20:41:01</t>
+          <t>2026-08-28 21:42:12</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28 20:41:01</t>
+          <t>2026-08-28 21:42:12</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-28 20:41:01</t>
+          <t>2026-08-28 21:42:12</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-28 20:41:01</t>
+          <t>2026-08-28 21:42:12</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-28 20:41:01</t>
+          <t>2026-08-28 21:42:12</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28 20:41:01</t>
+          <t>2026-08-28 21:42:12</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-28 20:41:01</t>
+          <t>2026-08-28 21:42:12</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-28 20:41:01</t>
+          <t>2026-08-28 21:42:12</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-28 20:41:01</t>
+          <t>2026-08-28 21:42:12</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-28 20:41:01</t>
+          <t>2026-08-28 21:42:12</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-28 20:41:01</t>
+          <t>2026-08-28 21:42:12</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-28 20:41:01</t>
+          <t>2026-08-28 21:42:12</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-28 20:41:03</t>
+          <t>2026-08-28 21:42:13</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28 20:41:03</t>
+          <t>2026-08-28 21:42:13</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28 20:41:03</t>
+          <t>2026-08-28 21:42:13</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28 20:41:03</t>
+          <t>2026-08-28 21:42:13</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28 20:41:03</t>
+          <t>2026-08-28 21:42:13</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28 20:41:03</t>
+          <t>2026-08-28 21:42:13</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28 20:41:03</t>
+          <t>2026-08-28 21:42:13</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-28 20:41:03</t>
+          <t>2026-08-28 21:42:13</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-28 20:41:03</t>
+          <t>2026-08-28 21:42:13</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-28 20:41:03</t>
+          <t>2026-08-28 21:42:13</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 20:41:03</t>
+          <t>2026-08-28 21:42:13</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-28 20:41:03</t>
+          <t>2026-08-28 21:42:13</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-28 20:41:03</t>
+          <t>2026-08-28 21:42:13</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-28 20:41:03</t>
+          <t>2026-08-28 21:42:13</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-28 20:41:03</t>
+          <t>2026-08-28 21:42:13</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-28 20:41:04</t>
+          <t>2026-08-28 21:42:14</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-28 20:41:04</t>
+          <t>2026-08-28 21:42:14</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-28 20:41:04</t>
+          <t>2026-08-28 21:42:14</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-28 20:41:04</t>
+          <t>2026-08-28 21:42:14</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-28 20:41:04</t>
+          <t>2026-08-28 21:42:14</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-28_00993A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-28_00993A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 21:42:10</t>
+          <t>2026-08-28 21:47:29</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 21:42:10</t>
+          <t>2026-08-28 21:47:29</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 21:42:10</t>
+          <t>2026-08-28 21:47:29</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 21:42:10</t>
+          <t>2026-08-28 21:47:29</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 21:42:10</t>
+          <t>2026-08-28 21:47:29</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 21:42:10</t>
+          <t>2026-08-28 21:47:29</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 21:42:10</t>
+          <t>2026-08-28 21:47:29</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 21:42:10</t>
+          <t>2026-08-28 21:47:29</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 21:42:10</t>
+          <t>2026-08-28 21:47:29</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 21:42:10</t>
+          <t>2026-08-28 21:47:29</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 21:42:10</t>
+          <t>2026-08-28 21:47:29</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 21:42:10</t>
+          <t>2026-08-28 21:47:29</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 21:42:10</t>
+          <t>2026-08-28 21:47:29</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 21:42:10</t>
+          <t>2026-08-28 21:47:29</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 21:42:10</t>
+          <t>2026-08-28 21:47:29</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-28 21:42:12</t>
+          <t>2026-08-28 21:47:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28 21:42:12</t>
+          <t>2026-08-28 21:47:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28 21:42:12</t>
+          <t>2026-08-28 21:47:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28 21:42:12</t>
+          <t>2026-08-28 21:47:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28 21:42:12</t>
+          <t>2026-08-28 21:47:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-28 21:42:12</t>
+          <t>2026-08-28 21:47:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-28 21:42:12</t>
+          <t>2026-08-28 21:47:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-28 21:42:12</t>
+          <t>2026-08-28 21:47:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28 21:42:12</t>
+          <t>2026-08-28 21:47:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-28 21:42:12</t>
+          <t>2026-08-28 21:47:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-28 21:42:12</t>
+          <t>2026-08-28 21:47:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-28 21:42:12</t>
+          <t>2026-08-28 21:47:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-28 21:42:12</t>
+          <t>2026-08-28 21:47:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-28 21:42:12</t>
+          <t>2026-08-28 21:47:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-28 21:42:12</t>
+          <t>2026-08-28 21:47:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-28 21:42:13</t>
+          <t>2026-08-28 21:47:32</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28 21:42:13</t>
+          <t>2026-08-28 21:47:32</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28 21:42:13</t>
+          <t>2026-08-28 21:47:32</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28 21:42:13</t>
+          <t>2026-08-28 21:47:32</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28 21:42:13</t>
+          <t>2026-08-28 21:47:32</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28 21:42:13</t>
+          <t>2026-08-28 21:47:32</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28 21:42:13</t>
+          <t>2026-08-28 21:47:32</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-28 21:42:13</t>
+          <t>2026-08-28 21:47:32</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-28 21:42:13</t>
+          <t>2026-08-28 21:47:32</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-28 21:42:13</t>
+          <t>2026-08-28 21:47:32</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 21:42:13</t>
+          <t>2026-08-28 21:47:32</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-28 21:42:13</t>
+          <t>2026-08-28 21:47:32</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-28 21:42:13</t>
+          <t>2026-08-28 21:47:32</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-28 21:42:13</t>
+          <t>2026-08-28 21:47:32</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-28 21:42:13</t>
+          <t>2026-08-28 21:47:32</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-28 21:42:14</t>
+          <t>2026-08-28 21:47:33</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-28 21:42:14</t>
+          <t>2026-08-28 21:47:33</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-28 21:42:14</t>
+          <t>2026-08-28 21:47:33</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-28 21:42:14</t>
+          <t>2026-08-28 21:47:33</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-28 21:42:14</t>
+          <t>2026-08-28 21:47:33</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
